--- a/servers/maze_main_server/conf.d/data/maze_attr_list_order_v8【迷宫-属性列表-排序】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attr_list_order_v8【迷宫-属性列表-排序】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31213901-9C75-4194-A863-3AB7F69E4E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62BAFBF8-A663-4318-948A-E23CF770C0FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -107,25 +107,43 @@
     <t>暴击几率</t>
   </si>
   <si>
+    <t>地下城复活时间</t>
+  </si>
+  <si>
     <t>复活时间</t>
   </si>
   <si>
     <t>暴击伤害</t>
   </si>
   <si>
+    <t>击中回血固定值</t>
+  </si>
+  <si>
     <t>击中敌人回复</t>
   </si>
   <si>
+    <t>火焰抗性</t>
+  </si>
+  <si>
     <t>[火焰]抗性</t>
   </si>
   <si>
-    <t>攻击范围</t>
-  </si>
-  <si>
-    <t>击中怪物回血</t>
-  </si>
-  <si>
-    <t>攻击数量</t>
+    <t>极寒抗性</t>
+  </si>
+  <si>
+    <t>[极寒]抗性</t>
+  </si>
+  <si>
+    <t>闪电抗性</t>
+  </si>
+  <si>
+    <t>[闪电]抗性</t>
+  </si>
+  <si>
+    <t>剧毒抗性</t>
+  </si>
+  <si>
+    <t>[剧毒]抗性</t>
   </si>
 </sst>
 </file>
@@ -496,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" customWidth="1"/>
@@ -594,7 +612,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>3010000</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
@@ -614,7 +632,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>3020000</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>19</v>
@@ -634,7 +652,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>3030000</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>20</v>
@@ -654,7 +672,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="1">
-        <v>3040901</v>
+        <v>10539</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>21</v>
@@ -674,10 +692,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="1">
-        <v>3041001</v>
+        <v>10538</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>22</v>
@@ -694,10 +712,10 @@
         <v>6</v>
       </c>
       <c r="D10" s="1">
-        <v>3041101</v>
+        <v>10536</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>23</v>
@@ -714,13 +732,13 @@
         <v>7</v>
       </c>
       <c r="D11" s="1">
-        <v>3041201</v>
+        <v>10531</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.15">
@@ -734,13 +752,13 @@
         <v>8</v>
       </c>
       <c r="D12" s="1">
-        <v>3041301</v>
+        <v>10537</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.15">
@@ -754,13 +772,13 @@
         <v>9</v>
       </c>
       <c r="D13" s="1">
-        <v>3041401</v>
+        <v>10559</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>20</v>
@@ -768,22 +786,82 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
-        <v>10010</v>
+        <v>20001</v>
       </c>
       <c r="B14" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D14" s="3">
-        <v>3041501</v>
+        <v>10519</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>27</v>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A15" s="1">
+        <v>20002</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2</v>
+      </c>
+      <c r="D15" s="3">
+        <v>10520</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A16" s="1">
+        <v>20003</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1">
+        <v>3</v>
+      </c>
+      <c r="D16" s="3">
+        <v>10521</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A17" s="1">
+        <v>20004</v>
+      </c>
+      <c r="B17" s="1">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1">
+        <v>4</v>
+      </c>
+      <c r="D17" s="3">
+        <v>10522</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_attr_list_order_v8【迷宫-属性列表-排序】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attr_list_order_v8【迷宫-属性列表-排序】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62BAFBF8-A663-4318-948A-E23CF770C0FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31213901-9C75-4194-A863-3AB7F69E4E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -107,43 +107,25 @@
     <t>暴击几率</t>
   </si>
   <si>
-    <t>地下城复活时间</t>
-  </si>
-  <si>
     <t>复活时间</t>
   </si>
   <si>
     <t>暴击伤害</t>
   </si>
   <si>
-    <t>击中回血固定值</t>
-  </si>
-  <si>
     <t>击中敌人回复</t>
   </si>
   <si>
-    <t>火焰抗性</t>
-  </si>
-  <si>
     <t>[火焰]抗性</t>
   </si>
   <si>
-    <t>极寒抗性</t>
-  </si>
-  <si>
-    <t>[极寒]抗性</t>
-  </si>
-  <si>
-    <t>闪电抗性</t>
-  </si>
-  <si>
-    <t>[闪电]抗性</t>
-  </si>
-  <si>
-    <t>剧毒抗性</t>
-  </si>
-  <si>
-    <t>[剧毒]抗性</t>
+    <t>攻击范围</t>
+  </si>
+  <si>
+    <t>击中怪物回血</t>
+  </si>
+  <si>
+    <t>攻击数量</t>
   </si>
 </sst>
 </file>
@@ -514,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" customWidth="1"/>
@@ -612,7 +594,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>19</v>
+        <v>3010000</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
@@ -632,7 +614,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>21</v>
+        <v>3020000</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>19</v>
@@ -652,7 +634,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>23</v>
+        <v>3030000</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>20</v>
@@ -672,7 +654,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="1">
-        <v>10539</v>
+        <v>3040901</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>21</v>
@@ -692,10 +674,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="1">
-        <v>10538</v>
+        <v>3041001</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>22</v>
@@ -712,10 +694,10 @@
         <v>6</v>
       </c>
       <c r="D10" s="1">
-        <v>10536</v>
+        <v>3041101</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>23</v>
@@ -732,13 +714,13 @@
         <v>7</v>
       </c>
       <c r="D11" s="1">
-        <v>10531</v>
+        <v>3041201</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.15">
@@ -752,13 +734,13 @@
         <v>8</v>
       </c>
       <c r="D12" s="1">
-        <v>10537</v>
+        <v>3041301</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.15">
@@ -772,13 +754,13 @@
         <v>9</v>
       </c>
       <c r="D13" s="1">
-        <v>10559</v>
+        <v>3041401</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>20</v>
@@ -786,82 +768,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
-        <v>20001</v>
+        <v>10010</v>
       </c>
       <c r="B14" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>10519</v>
+        <v>3041501</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A15" s="1">
-        <v>20002</v>
-      </c>
-      <c r="B15" s="1">
-        <v>2</v>
-      </c>
-      <c r="C15" s="1">
-        <v>2</v>
-      </c>
-      <c r="D15" s="3">
-        <v>10520</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A16" s="1">
-        <v>20003</v>
-      </c>
-      <c r="B16" s="1">
-        <v>2</v>
-      </c>
-      <c r="C16" s="1">
-        <v>3</v>
-      </c>
-      <c r="D16" s="3">
-        <v>10521</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A17" s="1">
-        <v>20004</v>
-      </c>
-      <c r="B17" s="1">
-        <v>2</v>
-      </c>
-      <c r="C17" s="1">
-        <v>4</v>
-      </c>
-      <c r="D17" s="3">
-        <v>10522</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
